--- a/reports/operating_manual/Financial_Path_Twin_운영_요약.xlsx
+++ b/reports/operating_manual/Financial_Path_Twin_운영_요약.xlsx
@@ -1310,7 +1310,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준 커밋: c68c8cc / 현재 로컬 Post-P0 보강: 있음 / 모든 숫자와 고객 ID는 합성 데이터 데모 기준</t>
+          <t>기준 커밋: 6744e96 / 현재 로컬 Post-P0 보강: 있음 / 모든 숫자와 고객 ID는 합성 데이터 데모 기준</t>
         </is>
       </c>
     </row>
